--- a/data/file_generation/reference/data_107/G店_揽收明细_res.xlsx
+++ b/data/file_generation/reference/data_107/G店_揽收明细_res.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0206/data_107/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/ai办公标注/output/data_107/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCFE5A1-A92F-2841-B28B-5AC17A1198EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D574B1-6B7C-0942-A3B1-59638C6EFFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="500" windowWidth="34760" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="72">
   <si>
     <t>运单编号</t>
   </si>
@@ -62,9 +62,6 @@
     <t>客户H</t>
   </si>
   <si>
-    <t>2025-10-01 15:15:20</t>
-  </si>
-  <si>
     <t>广西壮族自治区</t>
   </si>
   <si>
@@ -77,42 +74,27 @@
     <t>Z329QGO36IV2</t>
   </si>
   <si>
-    <t>2025-10-08 20:44:31</t>
-  </si>
-  <si>
     <t>山东省</t>
   </si>
   <si>
     <t>3DHZRWYUDNOV</t>
   </si>
   <si>
-    <t>2025-10-11 16:06:21</t>
-  </si>
-  <si>
     <t>59LFMZSPUB2Z</t>
   </si>
   <si>
-    <t>2025-10-11 16:08:06</t>
-  </si>
-  <si>
     <t>黑龙江省</t>
   </si>
   <si>
     <t>0TCUON3OJY1M</t>
   </si>
   <si>
-    <t>2025-10-11 19:18:36</t>
-  </si>
-  <si>
     <t>吉林省</t>
   </si>
   <si>
     <t>PNGXSV6CQOXJ</t>
   </si>
   <si>
-    <t>2025-10-11 19:18:41</t>
-  </si>
-  <si>
     <t>四川省</t>
   </si>
   <si>
@@ -122,57 +104,36 @@
     <t>JUSLPPJ7HVGT</t>
   </si>
   <si>
-    <t>2025-10-12 09:19:08</t>
-  </si>
-  <si>
     <t>甘肃省</t>
   </si>
   <si>
     <t>FQGMRCVKCYGU</t>
   </si>
   <si>
-    <t>2025-10-15 11:00:05</t>
-  </si>
-  <si>
     <t>5735SU71OD9N</t>
   </si>
   <si>
-    <t>2025-10-15 11:00:19</t>
-  </si>
-  <si>
     <t>ONBT2G0S1WIY</t>
   </si>
   <si>
-    <t>2025-10-16 11:09:06</t>
-  </si>
-  <si>
     <t>辽宁省</t>
   </si>
   <si>
     <t>AJL9Z1ZYKMTX</t>
   </si>
   <si>
-    <t>2025-10-16 11:09:07</t>
-  </si>
-  <si>
     <t>福建省</t>
   </si>
   <si>
     <t>XPH2413XJ35N</t>
   </si>
   <si>
-    <t>2025-10-24 08:01:51</t>
-  </si>
-  <si>
     <t>CGDNKJXGP81E</t>
   </si>
   <si>
     <t>W7WNXVPJSNCL</t>
   </si>
   <si>
-    <t>2025-10-24 08:05:11</t>
-  </si>
-  <si>
     <t>WESQGYXCDPKV</t>
   </si>
   <si>
@@ -185,24 +146,15 @@
     <t>C16X95M54BZ2</t>
   </si>
   <si>
-    <t>2025-10-24 09:09:03</t>
-  </si>
-  <si>
     <t>U4Y2FN769FCC</t>
   </si>
   <si>
-    <t>2025-10-27 11:04:17</t>
-  </si>
-  <si>
     <t>贵州省</t>
   </si>
   <si>
     <t>JPCZ4I4KTUP1</t>
   </si>
   <si>
-    <t>2025-10-28 13:47:28</t>
-  </si>
-  <si>
     <t>IGBPLD9NV1WX</t>
   </si>
   <si>
@@ -230,69 +182,39 @@
     <t>EFZ72Z01DPJ5</t>
   </si>
   <si>
-    <t>2025-10-28 19:22:40</t>
-  </si>
-  <si>
     <t>A2TV42D8RCXB</t>
   </si>
   <si>
-    <t>2025-10-28 19:23:47</t>
-  </si>
-  <si>
     <t>0SI667R285VU</t>
   </si>
   <si>
-    <t>2025-10-28 21:10:44</t>
-  </si>
-  <si>
     <t>S1YSFGLREQY8</t>
   </si>
   <si>
-    <t>2025-10-28 21:10:58</t>
-  </si>
-  <si>
     <t>Q6KMS9QSXJ7X</t>
   </si>
   <si>
-    <t>2025-10-30 09:34:37</t>
-  </si>
-  <si>
     <t>BO1XO7877JG2</t>
   </si>
   <si>
-    <t>2025-10-30 09:34:44</t>
-  </si>
-  <si>
     <t>LN125HYCDFTD</t>
   </si>
   <si>
-    <t>2025-10-04 11:13:10</t>
-  </si>
-  <si>
     <t>海南省</t>
   </si>
   <si>
     <t>U61LKFFI69KI</t>
   </si>
   <si>
-    <t>2025-10-28 19:22:48</t>
-  </si>
-  <si>
     <t>北京</t>
   </si>
   <si>
     <t>V7OAQ93W7BZX</t>
   </si>
   <si>
-    <t>2025-10-11 16:08:04</t>
-  </si>
-  <si>
     <t>KUI477ZOVGM5</t>
   </si>
   <si>
-    <t>2025-10-07 15:38:31</t>
-  </si>
-  <si>
     <t>NVEB22WQJOV3</t>
   </si>
   <si>
@@ -302,46 +224,31 @@
     <t>ZHU8XQ4QB1KL</t>
   </si>
   <si>
-    <t>2025-10-28 21:10:53</t>
-  </si>
-  <si>
     <t>EUDNT1LACHKB</t>
   </si>
   <si>
-    <t>2025-10-15 10:59:08</t>
-  </si>
-  <si>
     <t>LZ3W35V3Q7DP</t>
   </si>
   <si>
-    <t>2025-10-15 10:59:51</t>
-  </si>
-  <si>
     <t>SWHIYARHHSMH</t>
   </si>
   <si>
-    <t>2025-10-11 16:08:03</t>
-  </si>
-  <si>
     <t>YM0XV5AB5BMI</t>
   </si>
   <si>
-    <t>2025-10-16 11:09:05</t>
-  </si>
-  <si>
     <t>KAO94LSISMZ2</t>
   </si>
   <si>
     <t>RP307JNAB43S</t>
   </si>
   <si>
-    <t>2025-10-28 13:48:23</t>
-  </si>
-  <si>
     <t>青海省</t>
   </si>
   <si>
     <t>9SZP7ZHOSLJ5</t>
+  </si>
+  <si>
+    <t>2025年10月</t>
   </si>
 </sst>
 </file>
@@ -742,10 +649,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
       </c>
       <c r="E2">
         <v>0.7</v>
@@ -754,10 +661,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="I2">
         <f>ROUND(126.6-48*1.8,2)</f>
@@ -766,16 +673,16 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
       </c>
       <c r="E3">
         <v>0.7</v>
@@ -786,16 +693,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>0.3</v>
@@ -806,16 +713,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>0.79</v>
@@ -826,16 +733,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>0.67</v>
@@ -846,16 +753,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>0.49</v>
@@ -866,16 +773,16 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8">
         <v>0.72</v>
@@ -886,16 +793,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E9">
         <v>0.69</v>
@@ -906,16 +813,16 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>0.46</v>
@@ -926,16 +833,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>0.53</v>
@@ -946,16 +853,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E12">
         <v>0.69</v>
@@ -966,16 +873,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E13">
         <v>0.73</v>
@@ -986,16 +893,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E14">
         <v>0.26</v>
@@ -1006,16 +913,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>0.51</v>
@@ -1026,16 +933,16 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E16">
         <v>0.49</v>
@@ -1046,16 +953,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E17">
         <v>0.61</v>
@@ -1066,16 +973,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18">
         <v>0.69</v>
@@ -1086,16 +993,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>0.7</v>
@@ -1106,16 +1013,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E20">
         <v>0.7</v>
@@ -1126,16 +1033,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E21">
         <v>0.4</v>
@@ -1146,16 +1053,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E22">
         <v>0.2</v>
@@ -1166,16 +1073,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E23">
         <v>0.2</v>
@@ -1186,16 +1093,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E24">
         <v>0.65</v>
@@ -1206,16 +1113,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E25">
         <v>0.66</v>
@@ -1226,16 +1133,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E26">
         <v>0.67</v>
@@ -1246,16 +1153,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E27">
         <v>0.68</v>
@@ -1266,16 +1173,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E28">
         <v>0.69</v>
@@ -1286,16 +1193,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E29">
         <v>0.71</v>
@@ -1306,16 +1213,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E30">
         <v>0.69</v>
@@ -1326,16 +1233,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E31">
         <v>0.5</v>
@@ -1346,16 +1253,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E32">
         <v>0.62</v>
@@ -1366,7 +1273,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -1375,7 +1282,7 @@
         <v>71</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E33">
         <v>0.69</v>
@@ -1386,16 +1293,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E34">
         <v>0.67</v>
@@ -1406,16 +1313,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E35">
         <v>0.65</v>
@@ -1426,16 +1333,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="E36">
         <v>0.3</v>
@@ -1446,16 +1353,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E37">
         <v>0.5</v>
@@ -1466,16 +1373,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D38" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="E38">
         <v>0.56999999999999995</v>
@@ -1486,16 +1393,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="E39">
         <v>0.67</v>
@@ -1506,16 +1413,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
         <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E40">
         <v>1.01</v>
@@ -1526,16 +1433,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E41">
         <v>1.05</v>
@@ -1546,16 +1453,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s">
         <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E42">
         <v>1.07</v>
@@ -1566,16 +1473,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E43">
         <v>1.0900000000000001</v>
@@ -1586,16 +1493,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E44">
         <v>1.0900000000000001</v>
@@ -1606,16 +1513,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45">
         <v>1.1200000000000001</v>
@@ -1626,16 +1533,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E46">
         <v>1.1299999999999999</v>
@@ -1646,16 +1553,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E47">
         <v>1.44</v>
@@ -1666,16 +1573,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="E48">
         <v>1.99</v>
@@ -1686,16 +1593,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D49" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="E49">
         <v>2.04</v>
@@ -1874,13 +1781,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F373DD37-6EF5-45F8-8590-41E4EF0AB583}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A4991EB-C77F-495E-8A7D-8D6402286523}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3329FED-2EB6-4481-8A1F-1EDE68C83171}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0924EA31-6617-4FA2-804C-817BC6F9B0E1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{928FA68C-A6A2-4C12-92A5-0B6A9167B4BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{400A7D05-9291-4900-AB68-22E63540C09E}"/>
 </file>